--- a/data/Exter-Mada.xlsx
+++ b/data/Exter-Mada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8db62cf83fca7555/Bureau/My Paper Project/I-O modeling/Exter_Mada/GAMS Code/EXTER-MADA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8db62cf83fca7555/Bureau/My Paper Project/I-O modeling/Exter_Mada/GAMS Code/EXTER-MADA/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="8_{6D6915A7-1F54-4802-A4FC-9946BD8A267F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27147050-4CCC-4CB0-BB82-E834D3FBA0BA}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="8_{6D6915A7-1F54-4802-A4FC-9946BD8A267F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6AA7DEC-E6A4-4AF3-85CA-965D96043DEE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="945" xr2:uid="{C166FFEB-AA43-4878-87E5-4D9B41DEBF77}"/>
   </bookViews>
@@ -211,8 +211,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -663,10 +663,10 @@
   <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -704,67 +704,67 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1037,6 +1037,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2762,12 +2766,8 @@
       <c r="F21" s="48">
         <v>5806.4500396857466</v>
       </c>
-      <c r="G21" s="51">
-        <v>0</v>
-      </c>
-      <c r="H21" s="51">
-        <v>0</v>
-      </c>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="51"/>
       <c r="J21" s="51"/>
       <c r="K21" s="51"/>
@@ -2898,12 +2898,8 @@
       <c r="F23" s="29">
         <v>2631.99408735114</v>
       </c>
-      <c r="G23" s="32">
-        <v>0</v>
-      </c>
-      <c r="H23" s="32">
-        <v>0</v>
-      </c>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
       <c r="I23" s="59"/>
       <c r="J23" s="59"/>
       <c r="K23" s="59"/>
@@ -2968,12 +2964,8 @@
       <c r="F24" s="29">
         <v>24.508549265408757</v>
       </c>
-      <c r="G24" s="32">
-        <v>0</v>
-      </c>
-      <c r="H24" s="32">
-        <v>0</v>
-      </c>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
       <c r="I24" s="59"/>
       <c r="J24" s="59"/>
       <c r="K24" s="59"/>
@@ -3040,12 +3032,8 @@
       <c r="F25" s="29">
         <v>5571.3689828285369</v>
       </c>
-      <c r="G25" s="32">
-        <v>0</v>
-      </c>
-      <c r="H25" s="32">
-        <v>0</v>
-      </c>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
       <c r="I25" s="59"/>
       <c r="J25" s="59"/>
       <c r="K25" s="59"/>
@@ -3113,9 +3101,7 @@
       <c r="G26" s="32">
         <v>2181.5544426020888</v>
       </c>
-      <c r="H26" s="32">
-        <v>0</v>
-      </c>
+      <c r="H26" s="32"/>
       <c r="I26" s="69"/>
       <c r="J26" s="69"/>
       <c r="K26" s="69"/>
@@ -3176,9 +3162,7 @@
       <c r="D27" s="41"/>
       <c r="E27" s="78"/>
       <c r="F27" s="79"/>
-      <c r="G27" s="80">
-        <v>0</v>
-      </c>
+      <c r="G27" s="80"/>
       <c r="H27" s="80">
         <v>5527.8861625483132</v>
       </c>
